--- a/artfynd/S 3506-2024 artfynd.xlsx
+++ b/artfynd/S 3506-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY202"/>
+  <dimension ref="A1:AZ202"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123451861</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -867,6 +877,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102348585</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -965,6 +980,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102352010</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1063,6 +1083,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102348591</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1161,6 +1186,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102348631</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1259,6 +1289,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102352083</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1357,6 +1392,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102348630</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1455,6 +1495,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102348610</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1553,6 +1598,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102348633</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1659,6 +1709,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113668593</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1765,6 +1820,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113668594</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1871,6 +1931,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113668595</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1973,6 +2038,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113668599</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2075,6 +2145,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113668600</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2180,6 +2255,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113668602</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2289,6 +2369,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120096587</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2391,6 +2476,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123451717</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2493,6 +2583,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123451716</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2595,6 +2690,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123451722</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2697,6 +2797,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123451715</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2804,6 +2909,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120096604</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2911,6 +3021,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120096605</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3018,6 +3133,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120096607</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3125,6 +3245,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120096696</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3223,6 +3348,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102351828</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3321,6 +3451,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102350936</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3419,6 +3554,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102351672</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3517,6 +3657,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102351823</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3615,6 +3760,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102351880</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3722,6 +3872,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120096580</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3829,6 +3984,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120096581</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3936,6 +4096,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120096582</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4043,6 +4208,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120096583</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4150,6 +4320,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120096584</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4257,6 +4432,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127347852</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4355,6 +4535,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102349322</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4462,6 +4647,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120096609</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4569,6 +4759,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120096610</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4676,6 +4871,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120096611</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4774,6 +4974,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102348994</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4871,6 +5076,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116047515</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4969,6 +5179,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102349765</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5076,6 +5291,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120096615</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5183,6 +5403,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120096608</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5281,6 +5506,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102351638</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5388,6 +5618,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120096594</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5495,6 +5730,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120096596</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5602,6 +5842,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120096597</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5703,6 +5948,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102350972</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5800,6 +6050,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101818221</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5897,6 +6152,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101818222</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5994,6 +6254,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101818223</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6092,6 +6357,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102348779</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6190,6 +6460,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102348995</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6288,6 +6563,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102349666</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6386,6 +6666,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102351234</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6484,6 +6769,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102351584</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6581,6 +6871,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102887198</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6678,6 +6973,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102887227</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6775,6 +7075,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102887228</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6872,6 +7177,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102887229</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -6979,6 +7289,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120096669</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7086,6 +7401,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120096670</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7193,6 +7513,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120096671</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7300,6 +7625,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120096672</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7407,6 +7737,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120096673</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7514,6 +7849,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120096674</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7621,6 +7961,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120096675</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7728,6 +8073,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120096676</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7835,6 +8185,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120096677</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -7942,6 +8297,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120096678</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8049,6 +8409,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120096679</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8156,6 +8521,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120096680</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8263,6 +8633,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120096683</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8370,6 +8745,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120096684</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8477,6 +8857,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120096685</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8584,6 +8969,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120096686</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8691,6 +9081,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120096687</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8798,6 +9193,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120096688</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -8905,6 +9305,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120096689</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9012,6 +9417,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120096691</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9119,6 +9529,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120096692</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9226,6 +9641,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120096693</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9333,6 +9753,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120096694</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9440,6 +9865,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120096695</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9547,6 +9977,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120096661</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9654,6 +10089,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120096662</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -9761,6 +10201,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120096663</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -9859,6 +10304,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102348771</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -9957,6 +10407,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102351502</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -10064,6 +10519,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120096569</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -10171,6 +10631,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120096571</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -10278,6 +10743,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120096572</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -10385,6 +10855,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120096573</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -10492,6 +10967,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120096574</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -10599,6 +11079,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120096575</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -10706,6 +11191,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120096576</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -10813,6 +11303,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120096577</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -10920,6 +11415,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120096578</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -11017,6 +11517,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101818213</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -11115,6 +11620,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102349353</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -11213,6 +11723,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102349403</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -11311,6 +11826,11 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102349430</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -11409,6 +11929,11 @@
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102349466</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -11507,6 +12032,11 @@
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102349762</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -11605,6 +12135,11 @@
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102350704</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -11703,6 +12238,11 @@
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102351267</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -11801,6 +12341,11 @@
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102351352</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -11899,6 +12444,11 @@
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102351374</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -11997,6 +12547,11 @@
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102351463</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -12095,6 +12650,11 @@
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102351587</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -12192,6 +12752,11 @@
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102887199</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -12299,6 +12864,11 @@
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120096616</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -12406,6 +12976,11 @@
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120096618</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -12513,6 +13088,11 @@
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120096619</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -12620,6 +13200,11 @@
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120096620</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -12727,6 +13312,11 @@
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120096621</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -12834,6 +13424,11 @@
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120096622</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -12941,6 +13536,11 @@
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120096623</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -13048,6 +13648,11 @@
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120096624</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -13155,6 +13760,11 @@
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120096625</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -13262,6 +13872,11 @@
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120096626</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -13360,6 +13975,11 @@
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102349361</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -13458,6 +14078,11 @@
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102351278</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -13556,6 +14181,11 @@
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102351492</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -13663,6 +14293,11 @@
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120096599</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -13770,6 +14405,11 @@
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120096600</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -13877,6 +14517,11 @@
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120096601</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -13975,6 +14620,11 @@
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102351419</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -14073,6 +14723,11 @@
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102348895</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -14171,6 +14826,11 @@
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102349359</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -14269,6 +14929,11 @@
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
+      <c r="AZ133" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102349470</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -14367,6 +15032,11 @@
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
+      <c r="AZ134" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102349795</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -14465,6 +15135,11 @@
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
+      <c r="AZ135" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102351427</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -14572,6 +15247,11 @@
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
+      <c r="AZ136" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120096627</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -14679,6 +15359,11 @@
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
+      <c r="AZ137" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120096628</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -14786,6 +15471,11 @@
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
+      <c r="AZ138" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120096630</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -14895,6 +15585,11 @@
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
+      <c r="AZ139" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102350020</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -14997,6 +15692,11 @@
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
+      <c r="AZ140" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113396037</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -15099,6 +15799,11 @@
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
+      <c r="AZ141" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113668601</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -15206,6 +15911,11 @@
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
+      <c r="AZ142" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116047595</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -15327,6 +16037,11 @@
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
+      <c r="AZ143" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120096586</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -15439,6 +16154,11 @@
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
+      <c r="AZ144" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127347848</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -15551,6 +16271,11 @@
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
+      <c r="AZ145" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127347856</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -15663,6 +16388,11 @@
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
+      <c r="AZ146" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127347858</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -15779,6 +16509,11 @@
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
+      <c r="AZ147" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120096659</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -15893,6 +16628,11 @@
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
+      <c r="AZ148" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102377345</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -16014,6 +16754,11 @@
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
+      <c r="AZ149" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120096591</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -16130,6 +16875,11 @@
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
+      <c r="AZ150" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120096592</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -16246,6 +16996,11 @@
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
+      <c r="AZ151" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120096593</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -16356,6 +17111,11 @@
         </is>
       </c>
       <c r="AY152" t="inlineStr"/>
+      <c r="AZ152" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103956858</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -16470,6 +17230,11 @@
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
+      <c r="AZ153" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103956877</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -16567,6 +17332,11 @@
         </is>
       </c>
       <c r="AY154" t="inlineStr"/>
+      <c r="AZ154" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101818214</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -16664,6 +17434,11 @@
         </is>
       </c>
       <c r="AY155" t="inlineStr"/>
+      <c r="AZ155" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101818215</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -16761,6 +17536,11 @@
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
+      <c r="AZ156" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101818216</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -16858,6 +17638,11 @@
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
+      <c r="AZ157" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101818217</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -16977,6 +17762,11 @@
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
+      <c r="AZ158" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102887205</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -17096,6 +17886,11 @@
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>
+      <c r="AZ159" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102887216</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -17203,6 +17998,11 @@
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
+      <c r="AZ160" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120096647</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -17310,6 +18110,11 @@
         </is>
       </c>
       <c r="AY161" t="inlineStr"/>
+      <c r="AZ161" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120096648</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -17417,6 +18222,11 @@
         </is>
       </c>
       <c r="AY162" t="inlineStr"/>
+      <c r="AZ162" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120096649</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -17524,6 +18334,11 @@
         </is>
       </c>
       <c r="AY163" t="inlineStr"/>
+      <c r="AZ163" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120096650</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -17631,6 +18446,11 @@
         </is>
       </c>
       <c r="AY164" t="inlineStr"/>
+      <c r="AZ164" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120096651</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -17738,6 +18558,11 @@
         </is>
       </c>
       <c r="AY165" t="inlineStr"/>
+      <c r="AZ165" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120096652</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -17845,6 +18670,11 @@
         </is>
       </c>
       <c r="AY166" t="inlineStr"/>
+      <c r="AZ166" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120096653</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -17952,6 +18782,11 @@
         </is>
       </c>
       <c r="AY167" t="inlineStr"/>
+      <c r="AZ167" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120096655</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -18059,6 +18894,11 @@
         </is>
       </c>
       <c r="AY168" t="inlineStr"/>
+      <c r="AZ168" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120096656</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -18166,6 +19006,11 @@
         </is>
       </c>
       <c r="AY169" t="inlineStr"/>
+      <c r="AZ169" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120096657</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -18273,6 +19118,11 @@
         </is>
       </c>
       <c r="AY170" t="inlineStr"/>
+      <c r="AZ170" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120096658</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -18375,6 +19225,11 @@
         </is>
       </c>
       <c r="AY171" t="inlineStr"/>
+      <c r="AZ171" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123451804</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -18482,6 +19337,11 @@
         </is>
       </c>
       <c r="AY172" t="inlineStr"/>
+      <c r="AZ172" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127347847</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -18589,6 +19449,11 @@
         </is>
       </c>
       <c r="AY173" t="inlineStr"/>
+      <c r="AZ173" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127347850</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -18696,6 +19561,11 @@
         </is>
       </c>
       <c r="AY174" t="inlineStr"/>
+      <c r="AZ174" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127347851</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -18803,6 +19673,11 @@
         </is>
       </c>
       <c r="AY175" t="inlineStr"/>
+      <c r="AZ175" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127347853</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -18910,6 +19785,11 @@
         </is>
       </c>
       <c r="AY176" t="inlineStr"/>
+      <c r="AZ176" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127347854</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -19017,6 +19897,11 @@
         </is>
       </c>
       <c r="AY177" t="inlineStr"/>
+      <c r="AZ177" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127347855</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -19119,6 +20004,11 @@
         </is>
       </c>
       <c r="AY178" t="inlineStr"/>
+      <c r="AZ178" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123451813</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -19221,6 +20111,11 @@
         </is>
       </c>
       <c r="AY179" t="inlineStr"/>
+      <c r="AZ179" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123451812</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -19318,6 +20213,11 @@
         </is>
       </c>
       <c r="AY180" t="inlineStr"/>
+      <c r="AZ180" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101818209</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -19415,6 +20315,11 @@
         </is>
       </c>
       <c r="AY181" t="inlineStr"/>
+      <c r="AZ181" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101818210</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
@@ -19512,6 +20417,11 @@
         </is>
       </c>
       <c r="AY182" t="inlineStr"/>
+      <c r="AZ182" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101818211</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
@@ -19611,6 +20521,11 @@
         </is>
       </c>
       <c r="AY183" t="inlineStr"/>
+      <c r="AZ183" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102349490</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
@@ -19710,6 +20625,11 @@
         </is>
       </c>
       <c r="AY184" t="inlineStr"/>
+      <c r="AZ184" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102349672</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -19807,6 +20727,11 @@
         </is>
       </c>
       <c r="AY185" t="inlineStr"/>
+      <c r="AZ185" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102887204</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
@@ -19909,6 +20834,11 @@
         </is>
       </c>
       <c r="AY186" t="inlineStr"/>
+      <c r="AZ186" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123451805</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
@@ -20007,6 +20937,11 @@
         </is>
       </c>
       <c r="AY187" t="inlineStr"/>
+      <c r="AZ187" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102348782</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
@@ -20105,6 +21040,11 @@
         </is>
       </c>
       <c r="AY188" t="inlineStr"/>
+      <c r="AZ188" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102349159</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
@@ -20212,6 +21152,11 @@
         </is>
       </c>
       <c r="AY189" t="inlineStr"/>
+      <c r="AZ189" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120096631</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
@@ -20319,6 +21264,11 @@
         </is>
       </c>
       <c r="AY190" t="inlineStr"/>
+      <c r="AZ190" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120096632</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
@@ -20426,6 +21376,11 @@
         </is>
       </c>
       <c r="AY191" t="inlineStr"/>
+      <c r="AZ191" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120096633</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
@@ -20533,6 +21488,11 @@
         </is>
       </c>
       <c r="AY192" t="inlineStr"/>
+      <c r="AZ192" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120096634</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
@@ -20640,6 +21600,11 @@
         </is>
       </c>
       <c r="AY193" t="inlineStr"/>
+      <c r="AZ193" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120096635</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
@@ -20747,6 +21712,11 @@
         </is>
       </c>
       <c r="AY194" t="inlineStr"/>
+      <c r="AZ194" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120096636</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
@@ -20854,6 +21824,11 @@
         </is>
       </c>
       <c r="AY195" t="inlineStr"/>
+      <c r="AZ195" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120096639</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
@@ -20961,6 +21936,11 @@
         </is>
       </c>
       <c r="AY196" t="inlineStr"/>
+      <c r="AZ196" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120096640</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
@@ -21068,6 +22048,11 @@
         </is>
       </c>
       <c r="AY197" t="inlineStr"/>
+      <c r="AZ197" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120096641</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
@@ -21175,6 +22160,11 @@
         </is>
       </c>
       <c r="AY198" t="inlineStr"/>
+      <c r="AZ198" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120096644</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
@@ -21282,6 +22272,11 @@
         </is>
       </c>
       <c r="AY199" t="inlineStr"/>
+      <c r="AZ199" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120096645</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
@@ -21380,6 +22375,11 @@
         </is>
       </c>
       <c r="AY200" t="inlineStr"/>
+      <c r="AZ200" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102351399</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
@@ -21487,6 +22487,11 @@
         </is>
       </c>
       <c r="AY201" t="inlineStr"/>
+      <c r="AZ201" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120096660</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
@@ -21609,8 +22614,216 @@
         </is>
       </c>
       <c r="AY202" t="inlineStr"/>
+      <c r="AZ202" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120096646</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ145" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ146" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ147" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ148" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ149" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ150" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ151" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ152" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ153" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ154" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ155" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ156" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ157" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ158" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ159" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ160" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ161" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ162" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ163" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ164" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ165" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ166" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ167" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ168" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ169" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ170" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ171" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ172" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ173" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ174" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ175" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ176" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ177" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ178" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ179" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ180" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ181" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ182" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ183" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ184" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ185" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ186" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ187" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ188" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ189" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ190" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ191" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ192" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ193" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ194" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ195" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ196" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ197" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ198" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ199" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ200" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ201" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ202" r:id="rId201"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>